--- a/R8_B小_県学調_共通マスタ.xlsx
+++ b/R8_B小_県学調_共通マスタ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9149d06814ece6b4/github/survey-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C0A2CD-4C0D-4D9D-A9D7-E68F6FDF8C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{75C0A2CD-4C0D-4D9D-A9D7-E68F6FDF8C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{888A3153-F907-46D3-BB28-8A31EE12EE10}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="1500" windowWidth="23115" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6585" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="設定" sheetId="9" r:id="rId1"/>
@@ -1676,14 +1676,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD9245E-8831-4123-BD13-FF8AF2C9318B}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>209</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>211</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>215</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>217</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>218</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>219</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>220</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>221</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>222</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>224</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>225</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>226</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>228</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>231</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A16" t="s">
         <v>234</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A18" t="s">
         <v>238</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A19" t="s">
         <v>240</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A20" t="s">
         <v>242</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A21" t="s">
         <v>244</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>247</v>
       </c>
@@ -1935,17 +1935,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D793BDE-8574-4356-BF6F-65AC154CE378}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.125" customWidth="1"/>
-    <col min="15" max="15" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.2109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="9.35546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>144</v>
       </c>
@@ -1997,26 +1997,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB11B2AE-0D70-4AB4-BFB0-11A141A0BE7B}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:X11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="9.875" customWidth="1"/>
-    <col min="7" max="8" width="11.75" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="7" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.35546875" customWidth="1"/>
+    <col min="10" max="10" width="15.640625" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
-    <col min="12" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="14" width="21.375" customWidth="1"/>
-    <col min="15" max="15" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="11.75" customWidth="1"/>
+    <col min="12" max="13" width="18.35546875" customWidth="1"/>
+    <col min="14" max="14" width="21.35546875" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
     <col min="19" max="19" width="15.5" customWidth="1"/>
     <col min="20" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="12.125" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>65</v>
       </c>
@@ -2687,26 +2687,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DDAFA53-F3CB-4378-8E91-5D877C537815}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:X11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="9.875" customWidth="1"/>
-    <col min="7" max="8" width="11.75" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="7" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.35546875" customWidth="1"/>
+    <col min="10" max="10" width="15.640625" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
-    <col min="12" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="14" width="21.375" customWidth="1"/>
-    <col min="15" max="15" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="11.75" customWidth="1"/>
+    <col min="12" max="13" width="18.35546875" customWidth="1"/>
+    <col min="14" max="14" width="21.35546875" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
     <col min="19" max="19" width="15.5" customWidth="1"/>
     <col min="20" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="12.125" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>65</v>
       </c>
@@ -3377,26 +3377,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142A5F6B-4DA5-4D00-B8A6-7F5F6CBB99C0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:X4"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="9.875" customWidth="1"/>
-    <col min="7" max="8" width="11.75" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="7" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.35546875" customWidth="1"/>
+    <col min="10" max="10" width="15.640625" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
-    <col min="12" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="14" width="21.375" customWidth="1"/>
-    <col min="15" max="15" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="11.75" customWidth="1"/>
+    <col min="12" max="13" width="18.35546875" customWidth="1"/>
+    <col min="14" max="14" width="21.35546875" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
     <col min="19" max="19" width="15.5" customWidth="1"/>
     <col min="20" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="12.125" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -3678,16 +3678,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33C08DAF-9E90-4F71-B777-114760BC3106}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="9.875" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="15.640625" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.78515625" customWidth="1"/>
+    <col min="9" max="9" width="51.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>112</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -3745,7 +3746,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>142</v>
       </c>
@@ -3774,7 +3775,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>142</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>143</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>143</v>
       </c>
@@ -3890,7 +3891,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>143</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>261</v>
       </c>
@@ -3948,7 +3949,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>261</v>
       </c>
@@ -3977,7 +3978,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>261</v>
       </c>
@@ -4006,7 +4007,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>261</v>
       </c>
@@ -4035,7 +4036,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>262</v>
       </c>
@@ -4064,7 +4065,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>262</v>
       </c>
@@ -4093,7 +4094,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>262</v>
       </c>
@@ -4122,7 +4123,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A16" t="s">
         <v>262</v>
       </c>
@@ -4151,7 +4152,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A17" t="s">
         <v>262</v>
       </c>
@@ -4180,7 +4181,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A18" t="s">
         <v>262</v>
       </c>
@@ -4209,7 +4210,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A19" t="s">
         <v>262</v>
       </c>
@@ -4238,7 +4239,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A20" t="s">
         <v>262</v>
       </c>
@@ -4267,7 +4268,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A21" t="s">
         <v>262</v>
       </c>
@@ -4296,7 +4297,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>261</v>
       </c>
@@ -4325,7 +4326,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -4354,7 +4355,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.65">
       <c r="A24" t="s">
         <v>263</v>
       </c>
@@ -4397,15 +4398,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FF7FA5-7296-49F6-860E-D53F9AD71AA8}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="7" max="8" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.2109375" customWidth="1"/>
+    <col min="7" max="8" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>144</v>
       </c>
@@ -4443,7 +4444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>154</v>
       </c>
@@ -4460,7 +4461,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -4477,7 +4478,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -4494,7 +4495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -4511,7 +4512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>154</v>
       </c>
@@ -4562,7 +4563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>154</v>
       </c>
@@ -4579,7 +4580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -4602,7 +4603,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -4625,7 +4626,7 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>165</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -4671,7 +4672,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>165</v>
       </c>
@@ -4694,7 +4695,7 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>165</v>
       </c>
@@ -4717,7 +4718,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A16" t="s">
         <v>165</v>
       </c>
@@ -4740,7 +4741,7 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A17" t="s">
         <v>172</v>
       </c>
@@ -4763,7 +4764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A18" t="s">
         <v>172</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -4809,7 +4810,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A20" t="s">
         <v>172</v>
       </c>
@@ -4832,7 +4833,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A21" t="s">
         <v>172</v>
       </c>
@@ -4855,7 +4856,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>172</v>
       </c>
@@ -4878,7 +4879,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -4901,7 +4902,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A24" t="s">
         <v>172</v>
       </c>
@@ -4938,15 +4939,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F4895FB-DCE4-4A85-9E5A-4AEC336FFC02}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="7" max="8" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.2109375" customWidth="1"/>
+    <col min="7" max="8" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>144</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>154</v>
       </c>
@@ -5001,7 +5002,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -5035,7 +5036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -5052,7 +5053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -5069,7 +5070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -5086,7 +5087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>154</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>154</v>
       </c>
@@ -5120,7 +5121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -5143,7 +5144,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -5166,7 +5167,7 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>165</v>
       </c>
@@ -5189,7 +5190,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -5212,7 +5213,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>165</v>
       </c>
@@ -5235,7 +5236,7 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>165</v>
       </c>
@@ -5258,7 +5259,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A16" t="s">
         <v>165</v>
       </c>
@@ -5281,7 +5282,7 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A17" t="s">
         <v>172</v>
       </c>
@@ -5304,7 +5305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A18" t="s">
         <v>172</v>
       </c>
@@ -5327,7 +5328,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -5350,7 +5351,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A20" t="s">
         <v>172</v>
       </c>
@@ -5373,7 +5374,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A21" t="s">
         <v>172</v>
       </c>
@@ -5396,7 +5397,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>172</v>
       </c>
@@ -5419,7 +5420,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -5442,7 +5443,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A24" t="s">
         <v>172</v>
       </c>
@@ -5478,16 +5479,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0029B888-1AA8-48AC-86EA-2B51FBFF506D}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="7" max="8" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.2109375" customWidth="1"/>
+    <col min="7" max="8" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>144</v>
       </c>
@@ -5525,7 +5526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A2" t="s">
         <v>154</v>
       </c>
@@ -5542,7 +5543,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -5559,7 +5560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -5576,7 +5577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -5593,7 +5594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -5610,7 +5611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A7" t="s">
         <v>186</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A8" t="s">
         <v>186</v>
       </c>
@@ -5668,7 +5669,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -5697,7 +5698,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -5726,7 +5727,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A12" t="s">
         <v>186</v>
       </c>
@@ -5784,7 +5785,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A13" t="s">
         <v>186</v>
       </c>
@@ -5813,7 +5814,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A14" t="s">
         <v>186</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>186</v>
       </c>
@@ -5871,7 +5872,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A16" t="s">
         <v>186</v>
       </c>
@@ -5900,7 +5901,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A17" t="s">
         <v>186</v>
       </c>
@@ -5929,7 +5930,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A18" t="s">
         <v>186</v>
       </c>
@@ -5958,7 +5959,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A19" t="s">
         <v>186</v>
       </c>
@@ -5987,7 +5988,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A20" t="s">
         <v>186</v>
       </c>
@@ -6016,7 +6017,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.65">
       <c r="A21" t="s">
         <v>186</v>
       </c>
@@ -6058,21 +6059,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731ACD8B-3F3F-4FB8-AC79-3009D1AB82F2}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="2" max="3" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="10.25" customWidth="1"/>
+    <col min="2" max="3" width="10.2109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.2109375" customWidth="1"/>
+    <col min="9" max="9" width="11.35546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.2109375" customWidth="1"/>
+    <col min="16" max="16" width="10.2109375" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="20" max="20" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.2109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -6146,7 +6147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.65">
       <c r="A15" t="s">
         <v>86</v>
       </c>
